--- a/survey_templates/049_newspaper_survey--survey_templates.xlsx
+++ b/survey_templates/049_newspaper_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>time_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Time 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Which of the following?</t>
+          <t>Select5</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Which of the following?</t>
+          <t>Select6</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>date_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Date 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -937,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1140,29 +1140,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select4_choices</t>
+          <t>select5_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1174,12 +1174,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1191,29 +1191,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select5_choices</t>
+          <t>select6_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1242,46 +1242,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select6_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select6_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>option4</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>option4</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
